--- a/workbook/relations.xlsx
+++ b/workbook/relations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,8 +552,6 @@
           <t>sj</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>manual</t>
@@ -564,7 +562,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>dead</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -575,6 +573,3987 @@
       <c r="Q2" t="inlineStr">
         <is>
           <t>2026-09-30 00:15:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0431c8ee4e39</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>劉邦</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>p_lvhou</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>呂雉</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>夫</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>简介：劉邦之妻，臨朝稱制八年。</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>b38716070bcc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>p_zhouwu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>武王</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>p_zhougong</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>周公旦</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>简介：武王之弟，制禮作樂。</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5c4991f48e19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>p_simazhao</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>司馬昭</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>p_simayan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>司馬炎</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>简介：司馬昭之子，代魏建晉。</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>17764e4d7149</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>劉邦</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>p_hanhuidi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>劉盈</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>简介：劉邦與呂后之子。</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bee417f977f9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>p_lvhou</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>呂后</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>p_hanhuidi</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>劉盈</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>简介：劉邦與呂后之子。</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2c4c83a3c13f</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>p_liuxiang_hs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>劉向</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>p_liuxin_hs</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>劉歆</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>简介：劉向之子，倡古文經，後為王莽國師。</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>60f499b142ef</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>p_liufei</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>齊悼惠王</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>p_liuxingju</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>劉興居</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>简介：齊悼惠王之子，與誅諸呂，封濟北王，後謀反自殺。</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>594820affdd0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>p_simayao</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>孝武帝</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>p_simadezong</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>司馬德宗</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>简介：孝武帝子。</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>c678a3ac79cc</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>p_zhoubo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>周勃</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>p_zhouyafu</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>周亞夫</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>简介：周勃之子，平七國之亂。</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3c72972d2f9c</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>p_liushun</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>常山憲王</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>p_liubuyi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>劉不疑</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>简介：常山憲王之子，諡哀。</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>304f2001cedd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>p_jili</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>季歷</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>p_zhouwen</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>文王</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>简介：太王少子，文王之父。</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2078d05f6d16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>p_qin_huiwang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>秦惠王</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>p_chulizi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>樗里子</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>简介：秦惠王之弟，號智囊。</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>a02d1ec0804f</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>p_liuxi</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>城陽共王</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>p_liuyan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>劉延</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>简介：城陽共王之子，諡頃。</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>be1b5211ef1f</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>p_zhang_er</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>張耳</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>p_zhangao</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>張敖</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>简介：張耳之子，貫高之獄。</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>43e7c6df851c</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>p_zhaowuling</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>趙武靈王</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>p_wangzihe</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>王子何</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>简介：趙武靈王之子，名何，立為趙惠文王。</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>f4a897e40de2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>p_chupingwang</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>楚平王</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>p_baigongsheng</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>白公勝</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>祖父</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>简介：楚平王之孫，作亂，即白公。</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ce43d453585a</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>p_zhouwang</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>商紂王</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>p_wugeng</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>武庚</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>简介：商紂王之子，周初封於殷，與三監作亂被誅。</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cd0f2e4cee20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>p_sujian</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>蘇建</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>p_suwu</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>蘇武</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>简介：蘇武之父，從衛青出定襄。</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0041d2a87a1a</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>p_suqin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>蘇秦</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>p_sudai</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>蘇代</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>简介：蘇秦之弟，繼其縱橫之業。</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>56cea1d3bc79</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>p_liuzhang</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>城陽景王</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>p_liuxi</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>劉喜</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>简介：城陽景王之子，諡共。</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>672dcff37ed5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>p_lishiqi</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>酈食其</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>p_li_shang</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>酈商</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>简介：酈食其之弟。</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2630cf047652</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>p_liujiao</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>楚元王</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>p_liuli</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>劉禮</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>简介：楚元王之子，先封平陸侯，後立為楚王。</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>d5ad54ee2bb0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>p_tianying</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>田嬰</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>p_mengchangjun</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>孟嘗君</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>简介：齊威王少子，孟嘗君之父，號靖郭君。</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>26143b4b0b7e</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>p_zhugegang</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>諸葛亮</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>p_zhugezhan</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>諸葛瞻</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>简介：字思遠，諸葛亮之子。</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>c33396191064</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>p_liuchang</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>淮南厲王</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>p_liubo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>劉勃</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>简介：淮南厲王之子，先封衡山，後徙濟北，諡貞。</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>c8f87e56e196</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>p_liuwu</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>梁孝王</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>p_liuming</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>劉明</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>简介：梁孝王之子，謀反國除。</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>947974fe5e24</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>p_jinxiangong</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>晉獻公</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>p_xiqi</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>奚齊</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>简介：晉獻公與驪姬之子，為裏克所殺。</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>095dbe83fa70</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>p_liji</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>驪姬</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>p_xiqi</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>奚齊</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>简介：晉獻公與驪姬之子，為裏克所殺。</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>55f7899668f8</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>p_zhouwu</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>武王</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>p_guanshu</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>管叔鮮</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>简介：武王之弟，參與三監之亂。</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>e04f5111ff9b</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>p_weixian_hs</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>韋賢</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>p_weixuancheng</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>韋玄成</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>简介：韋賢之子，以讓爵於兄顯名，元帝時為相。</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>29f7917aa594</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>漢高祖</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>p_luyuangongzhu</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>魯元公主</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>简介：漢高祖之女，嫁張敖，張偃之母。</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4060d6c8bd5a</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>p_huzun</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>胡遵</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>p_x58047</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>胡奮</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>简介：魏將，胡奮之父。</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>25fae4c3e660</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>p_xiangyan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>項燕</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>p_xiangliang</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>項梁</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>简介：項梁之父，抗秦戰死，項羽之祖。</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>b9bbd151ef6f</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>p_zhuowangsun</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>卓王孫</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>p_zhuowenjun</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>卓文君</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>简介：卓文君之父，冶鐵致富。</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>291b93841321</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>p_banbiao</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>班彪</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>p_bangu</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>班固</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>简介：作《史記後傳》，班固之父。</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>e6b7b0388d08</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>p_chenligong</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>陳厲公</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>p_tianwan</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>陳完</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>简介：陳厲公之子，奔齊為田氏始祖。</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>56d8b05a2ff4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>p_suqin</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>蘇秦</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>p_suli</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>蘇厲</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>简介：蘇秦之弟，為燕說齊趙。</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3ee751ec022b</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>p_qinzhuangxiangwang</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>秦莊襄王</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>p_qinshihuang</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>秦始皇</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>简介：名子楚，秦始皇之父，呂不韋所立。</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>03f6fbc1a2b8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>p_mengtian</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>蒙恬</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>p_mengyi</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>蒙毅</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>简介：蒙恬之弟，為趙高所害。</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>22c9ec54ff6d</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>p_laoshang</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>老上單于</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>p_junchen</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>軍臣單于</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>简介：老上單于之子，與漢和親復又犯邊。</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>127a1274d490</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>p_xiahouyuan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>夏侯淵</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>p_xiahouda_sg</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>夏侯霸</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>简介：字仲權，夏侯淵之子。</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>8b180e1a5460</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>p_zhangao</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>張敖</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>p_luyuanwang</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>魯元王</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>简介：名張偃，張敖與魯元公主之子，呂后封為魯王。</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>b379679feff3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>p_luyuangongzhu</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>魯元公主</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>p_luyuanwang</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>魯元王</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>简介：名張偃，張敖與魯元公主之子，呂后封為魯王。</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>674d6f1b21b3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>p_jibu</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>季布</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>p_jixin2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>季心</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>简介：季布之弟，以勇聞關中。</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>7d7a81fbf4e3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>p_yuanan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>袁安</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>p_yuantang</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>袁湯</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>简介：字仲河，袁安之子。</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6aeb9b2e282d</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>p_simadan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>司馬談</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>p_simaqian</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>司馬遷</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>简介：司馬遷之父，臨終囑託著史。</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7d85ad627dd2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>p_modu</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>冒頓</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>p_laoshang</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>老上單于</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>简介：冒頓之子，數寇邊。</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>04e722951489</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>p_jinwengong</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>晉文公</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>p_gongziyong</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>公子雍</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>简介：晉文公之子，秦欲納之。</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12c88e64bc54</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>劉邦</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>p_liujian</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>劉建</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>简介：劉邦之子。</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>513231982081</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>p_qiyiwang</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>齊懿王</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>p_liucijing</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>劉次景</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>简介：齊懿王之子，齊悼惠王世家所見末代齊王。</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>e5d8ea6f360d</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>p_meicheng</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>枚乘</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>p_meigao</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>枚皋</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>简介：枚乘之子，善為賦。</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>6447d383f0d9</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>p_liujiao</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>劉交</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>p_liuyingke</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>劉郢客</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>简介：劉交之子，好詩書。</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>8c6c3c9ecfaa</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>p_weixuangong</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>衛宣公</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>p_gongzishou</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>公子壽</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>简介：衛宣公之子，為救急子而死。</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>37ac3c6bee55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>p_jinyougong</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>晉幽公</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>p_gongzizhi</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>公子止</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>简介：晉幽公之子，名止，立為晉烈公。</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>58d517381a99</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>p_wangliao</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>吳王僚</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>p_gongzigai</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>公子蓋</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>简介：吳王僚之弟，即公子蓋餘。</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>342dc567a405</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>p_weiman</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>衛滿</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>p_weiyouqu</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>衛右渠</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>祖父</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>简介：衛滿之孫，拒漢通使。</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>e56bd1502bf7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>p_huanjie_sg</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>桓階</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>p_huanjia_sg</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>桓嘉</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>简介：桓階之子。</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>9b2ff36f8bb8</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>p_jinhuigong</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>晉惠公</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>p_gongziyu</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>公子圉</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>简介：晉惠公之子，質於秦，後立為晉懷公。</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>b6081611ae10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>p_gongsunjiu</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>公孫糾</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>p_songzhaogong</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>宋昭公</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>简介：宋昭公之父。</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>c3c9b743e2de</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>p_liushun</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>常山憲王</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>p_liuchao</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>劉朝</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>简介：常山憲王之子，元氏王。</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>579ee52bae5e</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>p_caocao</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>曹操</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>p_caohuanghou</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>曹節</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>简介：獻帝皇后，曹操之女。</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>b64517dc20ef</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>p_caiyong</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>蔡邕</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>p_caiwenji</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>蔡文姬</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>简介：蔡邕之女，名琰。</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:31:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2296f0696b2f</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>劉邦</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>p_hanhuidi</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>劉盈</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>種子：劉邦之子劉盈（見本紀）</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:33:01</t>
         </is>
       </c>
     </row>

--- a/workbook/relations.xlsx
+++ b/workbook/relations.xlsx
@@ -1308,13 +1308,23 @@
       <c r="H14" t="n">
         <v>1</v>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>9790fe5d27b8</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>樗里子者，名疾，秦惠王之弟也，與惠王異母。</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1323,7 +1333,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>简介：秦惠王之弟，號智囊。</t>
+          <t>简介：秦惠王之弟，號智囊。 自动取证（硬句式）：「秦惠王 之弟」＝樗里子 对 秦惠王 的称呼，与边一致</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2820,13 +2830,23 @@
       <c r="H38" t="n">
         <v>0</v>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5155e2ddac34</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>陳完者，陳厲公他之子也。</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2835,7 +2855,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>简介：陳厲公之子，奔齊為田氏始祖。</t>
+          <t>简介：陳厲公之子，奔齊為田氏始祖。 自动取证（硬句式）：「陳厲公 之子」＝陳完 对 陳厲公 的称呼，与边一致</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -2883,13 +2903,23 @@
       <c r="H39" t="n">
         <v>1</v>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>d64718730c82</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>蘇秦之弟曰代，代弟蘇厲，見兄遂，亦皆學。</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2898,7 +2928,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>简介：蘇秦之弟，為燕說齊趙。</t>
+          <t>简介：蘇秦之弟，為燕說齊趙。 自动取证（硬句式）：「蘇秦 之弟」＝蘇厲 对 蘇秦 的称呼，与边一致</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4531,8 +4561,6 @@
           <t>sj</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>manual</t>

--- a/workbook/relations.xlsx
+++ b/workbook/relations.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="relations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="relation_evidence" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,7 +878,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>dead</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1333,7 +1334,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>简介：秦惠王之弟，號智囊。 自动取证（硬句式）：「秦惠王 之弟」＝樗里子 对 秦惠王 的称呼，与边一致</t>
+          <t>简介：秦惠王之弟，號智囊。 自动取证（硬句式）：「秦惠王 之弟」＝樗里子 对 秦惠王 的称呼，与边一致 自动取证（硬句式）：「秦惠王 之弟」＝樗里子 对 秦惠王 的称呼，与边一致 自动取证（硬句式）：「秦惠王 之弟」＝樗里子 对 秦惠王 的称呼，与边一致</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2336,7 +2337,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>dead</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2855,7 +2856,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>简介：陳厲公之子，奔齊為田氏始祖。 自动取证（硬句式）：「陳厲公 之子」＝陳完 对 陳厲公 的称呼，与边一致</t>
+          <t>简介：陳厲公之子，奔齊為田氏始祖。 自动取证（硬句式）：「陳厲公 之子」＝陳完 对 陳厲公 的称呼，与边一致 自动取证（硬句式）：「陳厲公 之子」＝陳完 对 陳厲公 的称呼，与边一致 自动取证（硬句式）：「陳厲公 之子」＝陳完 对 陳厲公 的称呼，与边一致</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -2903,23 +2904,15 @@
       <c r="H39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>d64718730c82</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>蘇秦之弟曰代，代弟蘇厲，見兄遂，亦皆學。</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2928,7 +2921,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>简介：蘇秦之弟，為燕說齊趙。 自动取证（硬句式）：「蘇秦 之弟」＝蘇厲 对 蘇秦 的称呼，与边一致</t>
+          <t>简介：蘇秦之弟，為燕說齊趙。 自动取证（硬句式）：「蘇秦 之弟」＝蘇厲 对 蘇秦 的称呼，与边一致 证据已撤：證據句「蘇秦之弟曰代，代弟蘇厲」說的是代的弟弟，蘇厲隔了一層，支撐不了這條邊（docs/28 P1-1）</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3301,7 +3294,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>dead</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3427,7 +3420,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>dead</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4582,6 +4575,353 @@
       <c r="Q65" t="inlineStr">
         <is>
           <t>2026-09-30 06:33:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>84e131974ee2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>p_lvhou</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>呂后</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>p_hanhuidi</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>劉盈</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>母</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>母系：劉邦與呂后之子，母為呂后（docs/28 P0-2）</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:14:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>b5f70ff6eb7f</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>p_liji</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>驪姬</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>p_xiqi</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>奚齊</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>母</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>母系：晉獻公與驪姬之子（docs/28 P0-2）</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:14:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>c212cf2c0cd1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>p_luyuangongzhu</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>魯元公主</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>p_luyuanwang</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>魯元王</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>母</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>母系：張敖與魯元公主之子（docs/28 P0-2）</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>6c89ba2115a3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>p_yuanan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>袁安</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>p_yuantang</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>袁湯</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>祖父</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>據 hhs-45「子彭」+「彭弟湯」：湯為彭之弟、袁京之子，即袁安之孫；原作「父」係簡介有誤（docs/28 P0-3）</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:15:13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rel_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>证据uid</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>判定(verdict)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>备注(note)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>录入时间(createdAt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2078d05f6d16</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>9790fe5d27b8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:37:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>e6b7b0388d08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5155e2ddac34</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:37:51</t>
         </is>
       </c>
     </row>

--- a/workbook/relations.xlsx
+++ b/workbook/relations.xlsx
@@ -553,6 +553,16 @@
           <t>sj</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>d05e46b3ac04</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>孝惠皇帝，高祖太子也，母曰呂皇后。</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>manual</t>
@@ -568,7 +578,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>P6-0 自檢關係</t>
+          <t>種子：劉邦之子劉盈（見本紀） 人工判定：高祖 名后紧接「子」（未带「之」） 人工判定：高祖 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -679,13 +689,23 @@
       <c r="H4" t="n">
         <v>1</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0dabbce7bd2a</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>周公旦者，周武王弟也。</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -694,7 +714,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>简介：武王之弟，制禮作樂。</t>
+          <t>简介：武王之弟，制禮作樂。 人工判定（2 条）：周武王 名后紧接「弟」（未带「之」） 人工判定（2 条）：周武王 名后紧接「弟」（未带「之」）</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -742,13 +762,23 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>f3596caac622</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>武帝泰始元年十二月丙寅，受禪，丁卯，追尊皇祖宣王為宣皇帝，伯考景王為景皇帝，考文王為文皇帝，宣王妃張氏為宣穆皇后，景王夫人羊氏為景皇后。</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -757,7 +787,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>简介：司馬昭之子，代魏建晉。</t>
+          <t>简介：司馬昭之子，代魏建晉。 人工判定：句里还有 2 个人，「之X」可能指别人 人工判定：句里还有 2 个人，「之X」可能指别人</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -994,13 +1024,23 @@
       <c r="H9" t="n">
         <v>0</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ad5c52ae44d6</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>濟北王興居，齊悼惠王子，以東牟侯助大臣誅諸呂，功少。</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1009,7 +1049,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>简介：齊悼惠王之子，與誅諸呂，封濟北王，後謀反自殺。</t>
+          <t>简介：齊悼惠王之子，與誅諸呂，封濟北王，後謀反自殺。 人工判定（2 条）：齊悼惠王 名后紧接「子」（未带「之」） 人工判定（2 条）：齊悼惠王 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1120,13 +1160,23 @@
       <c r="H11" t="n">
         <v>0</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>d51e3368d8a2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>絕一歲，文帝乃擇絳侯勃子賢者河內守亞夫，封為條侯，續絳侯後。</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1135,7 +1185,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>简介：周勃之子，平七國之亂。</t>
+          <t>简介：周勃之子，平七國之亂。 人工判定：絳侯 名后紧接「子」（未带「之」） 人工判定：絳侯 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1246,13 +1296,23 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>21bda05a5dd4</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>公季卒，子昌立，是為西伯。</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1261,7 +1321,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>简介：太王少子，文王之父。</t>
+          <t>简介：太王少子，文王之父。 人工判定：公季 名后紧接「子」（未带「之」） 人工判定：公季 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1445,13 +1505,23 @@
       <c r="H16" t="n">
         <v>0</v>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>d7d51d2ebc9c</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>趙王張敖始，耳子。</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1460,7 +1530,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>简介：張耳之子，貫高之獄。</t>
+          <t>简介：張耳之子，貫高之獄。 人工判定： 人工判定：</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1571,13 +1641,23 @@
       <c r="H18" t="n">
         <v>0</v>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7f6676806412</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>惠王二年，子西召故平王太子建之子勝於呉，以爲巣大夫，號曰白公。</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1586,7 +1666,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>简介：楚平王之孫，作亂，即白公。</t>
+          <t>简介：楚平王之孫，作亂，即白公。 人工判定：仅共现（间隔 17 字） 人工判定：仅共现（间隔 17 字）</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1634,13 +1714,23 @@
       <c r="H19" t="n">
         <v>0</v>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>9eeb5f3fe7a0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>封紂子武庚祿父，以續殷祀，令修行盤庚之政。</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1649,7 +1739,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>简介：商紂王之子，周初封於殷，與三監作亂被誅。</t>
+          <t>简介：商紂王之子，周初封於殷，與三監作亂被誅。 人工判定（2 条）：紂 名后紧接「子」（未带「之」） 人工判定（2 条）：紂 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1886,13 +1976,23 @@
       <c r="H23" t="n">
         <v>1</v>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>f9a3c6c1d2d9</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>酈生言其弟酈商，使將數千人從沛公西南略地。</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1901,7 +2001,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>简介：酈食其之弟。</t>
+          <t>简介：酈食其之弟。 人工判定（2 条）：酈生 名后紧接「弟」（未带「之」）；句里还有 1 个人，「之X」可能指别人 人工判定（2 条）：酈生 名后紧接「弟」（未带「之」）；句里还有 1 个人，「之X」可能指别人</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2012,13 +2112,23 @@
       <c r="H25" t="n">
         <v>0</v>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>dc45c9908f46</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>七年，齊孟嘗君父田嬰欺楚，楚威王伐齊，敗之於徐州，而令齊必逐田嬰。</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2027,7 +2137,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>简介：齊威王少子，孟嘗君之父，號靖郭君。</t>
+          <t>简介：齊威王少子，孟嘗君之父，號靖郭君。 人工判定：紧邻共现（间隔 6 字） 人工判定：紧邻共现（间隔 6 字）</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2201,13 +2311,23 @@
       <c r="H28" t="n">
         <v>0</v>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>825c2a43cf30</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>濟川王明者，梁孝王子，以桓邑侯孝景中六年為濟川王。</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2216,7 +2336,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>简介：梁孝王之子，謀反國除。</t>
+          <t>简介：梁孝王之子，謀反國除。 人工判定：梁孝王 名后紧接「子」（未带「之」） 人工判定：梁孝王 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2390,13 +2510,23 @@
       <c r="H31" t="n">
         <v>1</v>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>5ab10eb5eb7f</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>管叔鮮、蔡叔度者，周文王子而武王弟也。</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2405,7 +2535,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>简介：武王之弟，參與三監之亂。</t>
+          <t>简介：武王之弟，參與三監之亂。 人工判定（2 条）：武王 名后紧接「弟」（未带「之」）；句里还有 2 个人，「之X」可能指别人 人工判定（2 条）：武王 名后紧接「弟」（未带「之」）；句里还有 2 个人，「之X」可能指别人</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2516,13 +2646,23 @@
       <c r="H33" t="n">
         <v>0</v>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>c9c0210c3bed</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>子敖嗣立為王，尚高祖長女魯元公主，為王后。</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2531,7 +2671,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>简介：漢高祖之女，嫁張敖，張偃之母。</t>
+          <t>简介：漢高祖之女，嫁張敖，張偃之母。 人工判定：高祖 名后紧接「女」（未带「之」） 人工判定：高祖 名后紧接「女」（未带「之」）</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2642,13 +2782,23 @@
       <c r="H35" t="n">
         <v>0</v>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>d478de4c5a78</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>其季父項梁，梁父即楚將項燕，為秦將王翦所戮者也。</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2657,7 +2807,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>简介：項梁之父，抗秦戰死，項羽之祖。</t>
+          <t>简介：項梁之父，抗秦戰死，項羽之祖。 人工判定：紧邻共现（间隔 10 字）；句里还有 1 个人，「之X」可能指别人 人工判定：紧邻共现（间隔 10 字）；句里还有 1 个人，「之X」可能指别人</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2705,13 +2855,23 @@
       <c r="H36" t="n">
         <v>0</v>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>e33dc12855bd</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>是時卓王孫有女文君新寡，好音，故相如繆與令相重，而以琴心挑之。</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2720,7 +2880,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>简介：卓文君之父，冶鐵致富。</t>
+          <t>简介：卓文君之父，冶鐵致富。 人工判定（2 条）：卓王孫 名后紧接「女」（未带「之」） 人工判定（2 条）：卓王孫 名后紧接「女」（未带「之」）</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2969,13 +3129,23 @@
       <c r="H40" t="n">
         <v>0</v>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1e15d7d610e5</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>秦始皇帝者，秦莊襄王子也。</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2984,7 +3154,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>简介：名子楚，秦始皇之父，呂不韋所立。</t>
+          <t>简介：名子楚，秦始皇之父，呂不韋所立。 人工判定：秦莊襄王 名后紧接「子」（未带「之」） 人工判定：秦莊襄王 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3095,13 +3265,23 @@
       <c r="H42" t="n">
         <v>0</v>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>32e9d9b70603</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>後四年，老上單于死，子軍臣單于立，而中行說復事之。</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3110,7 +3290,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>简介：老上單于之子，與漢和親復又犯邊。</t>
+          <t>简介：老上單于之子，與漢和親復又犯邊。 人工判定：老上單于 名后紧接「子」（未带「之」）；句里还有 1 个人，「之X」可能指别人 人工判定：老上單于 名后紧接「子」（未带「之」）；句里还有 1 个人，「之X」可能指别人</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3221,13 +3401,23 @@
       <c r="H44" t="n">
         <v>0</v>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>551d7ad399d7</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>宣平侯張敖卒，以子偃為魯王，敖賜謚為魯元王。</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3236,7 +3426,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>简介：名張偃，張敖與魯元公主之子，呂后封為魯王。</t>
+          <t>简介：名張偃，張敖與魯元公主之子，呂后封為魯王。 人工判定：張敖 名后紧接「子」（未带「之」） 人工判定：張敖 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3347,13 +3537,23 @@
       <c r="H46" t="n">
         <v>1</v>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>d89d727126c9</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>季布弟季心，氣蓋關中，遇人恭謹，爲任俠，方數千里，士皆爭爲之死。</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3362,7 +3562,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>简介：季布之弟，以勇聞關中。</t>
+          <t>简介：季布之弟，以勇聞關中。 人工判定：季布 名后紧接「弟」（未带「之」） 人工判定：季布 名后紧接「弟」（未带「之」）</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3536,13 +3736,23 @@
       <c r="H49" t="n">
         <v>0</v>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>8aa658110370</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>後頃之，冒頓死，子稽粥立，號曰老上單于。</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3551,7 +3761,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>简介：冒頓之子，數寇邊。</t>
+          <t>简介：冒頓之子，數寇邊。 人工判定（2 条）：冒頓 名后紧接「子」（未带「之」） 人工判定（2 条）：冒頓 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -3662,13 +3872,23 @@
       <c r="H51" t="n">
         <v>0</v>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ac707229dd5c</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>復殺高祖子趙幽王友、共王恢及燕靈王建。</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3677,7 +3897,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>简介：劉邦之子。</t>
+          <t>简介：劉邦之子。 人工判定：高祖 名后紧接「子」（未带「之」）；句里还有 1 个人，「之X」可能指别人 人工判定：高祖 名后紧接「子」（未带「之」）；句里还有 1 个人，「之X」可能指别人</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -3725,13 +3945,23 @@
       <c r="H52" t="n">
         <v>0</v>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>5a54239d19bc</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>齊懿王立二十二年卒，子次景立，是為厲王。</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3740,7 +3970,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>简介：齊懿王之子，齊悼惠王世家所見末代齊王。</t>
+          <t>简介：齊懿王之子，齊悼惠王世家所見末代齊王。 人工判定：齊懿王 名后紧接「子」（未带「之」） 人工判定：齊懿王 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4418,13 +4648,23 @@
       <c r="H63" t="n">
         <v>0</v>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>6714a14a064b</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>獻穆曹皇后諱節，魏公曹操之中女也。</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4433,7 +4673,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>简介：獻帝皇后，曹操之女。</t>
+          <t>简介：獻帝皇后，曹操之女。 人工判定：魏公 名后紧接「女」（未带「之」） 人工判定：魏公 名后紧接「女」（未带「之」）</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -4481,13 +4721,23 @@
       <c r="H64" t="n">
         <v>0</v>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>6a3e534502c0</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>陳留董祀妻者，同郡蔡邕之女也，名琰，字文姬。</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4496,7 +4746,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>简介：蔡邕之女，名琰。</t>
+          <t>简介：蔡邕之女，名琰。 人工判定：「蔡邕 之女」＝董祀妻 对 蔡邕 的称呼，与边一致 人工判定：「蔡邕 之女」＝董祀妻 对 蔡邕 的称呼，与边一致</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -4554,13 +4804,23 @@
           <t>sj</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>d05e46b3ac04</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>孝惠皇帝，高祖太子也，母曰呂皇后。</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4569,7 +4829,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>種子：劉邦之子劉盈（見本紀）</t>
+          <t>種子：劉邦之子劉盈（見本紀） 人工判定：高祖 名后紧接「子」（未带「之」） 人工判定：高祖 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -4617,13 +4877,23 @@
       <c r="H66" t="n">
         <v>0</v>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>d05e46b3ac04</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>孝惠皇帝，高祖太子也，母曰呂皇后。</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4632,7 +4902,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>母系：劉邦與呂后之子，母為呂后（docs/28 P0-2）</t>
+          <t>母系：劉邦與呂后之子，母為呂后（docs/28 P0-2） 人工判定：人工指定 人工判定：人工指定</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -4680,13 +4950,23 @@
       <c r="H67" t="n">
         <v>0</v>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fedc3d41cf85</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>獻公與驪姬子奚齊居絳。</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4695,7 +4975,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>母系：晉獻公與驪姬之子（docs/28 P0-2）</t>
+          <t>母系：晉獻公與驪姬之子（docs/28 P0-2） 人工判定（2 条）：驪姬 名后紧接「子」（未带「之」） 人工判定（2 条）：驪姬 名后紧接「子」（未带「之」）</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -4841,7 +5121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4925,6 +5205,951 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>b38716070bcc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0dabbce7bd2a</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>b38716070bcc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>f0c400b4ae5b</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>武王 名后紧接「弟」（未带「之」）</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5c4991f48e19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>f3596caac622</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>60f499b142ef</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ad5c52ae44d6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>60f499b142ef</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9deedfeb5b80</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>齊悼惠王 名后紧接「子」（未带「之」）</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>c678a3ac79cc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>d51e3368d8a2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>304f2001cedd</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21bda05a5dd4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>be1b5211ef1f</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>d7d51d2ebc9c</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>f4a897e40de2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7f6676806412</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ce43d453585a</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>9eeb5f3fe7a0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ce43d453585a</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>189ef150b907</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>商紂 名后紧接「子」（未带「之」）</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>672dcff37ed5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>f9a3c6c1d2d9</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>672dcff37ed5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>84b1766343fe</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>酈生 名后紧接「弟」（未带「之」）；句里还有 1 个人，「之X」可能指别人</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>d5ad54ee2bb0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>dc45c9908f46</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>c8f87e56e196</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>825c2a43cf30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>55f7899668f8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5ab10eb5eb7f</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>55f7899668f8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>80ab7ac1c93a</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>武王 名后紧接「弟」（未带「之」）；句里还有 2 个人，「之X」可能指别人</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>29f7917aa594</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>c9c0210c3bed</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>25fae4c3e660</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>d478de4c5a78</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>b9bbd151ef6f</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>e33dc12855bd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>b9bbd151ef6f</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7ac8538857d5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>卓王孫 名后紧接「女」（未带「之」）</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3ee751ec022b</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1e15d7d610e5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>22c9ec54ff6d</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>32e9d9b70603</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>8b180e1a5460</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>551d7ad399d7</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>674d6f1b21b3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>d89d727126c9</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7d85ad627dd2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>8aa658110370</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>7d85ad627dd2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>a670642c948c</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>冒頓 名后紧接「子」（未带「之」）</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12c88e64bc54</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ac707229dd5c</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>513231982081</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5a54239d19bc</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>579ee52bae5e</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6714a14a064b</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>b64517dc20ef</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6a3e534502c0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2296f0696b2f</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>d05e46b3ac04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>84e131974ee2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>d05e46b3ac04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>b5f70ff6eb7f</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fedc3d41cf85</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>b5f70ff6eb7f</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1c3b3505ada5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>驪姬 名后紧接「子」（未带「之」）</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbook/relations.xlsx
+++ b/workbook/relations.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2719,13 +2719,23 @@
       <c r="H34" t="n">
         <v>0</v>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>8634ecc807d8</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>胡奮，字玄威，安定臨涇人也，魏車騎將軍陰密侯遵之子也。</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2734,7 +2744,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>简介：魏將，胡奮之父。</t>
+          <t>简介：魏將，胡奮之父。 人工判定：人工指定</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3064,8 +3074,6 @@
       <c r="H39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>auto-summary</t>
@@ -4522,13 +4530,23 @@
       <c r="H61" t="n">
         <v>0</v>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>bc3b23e76a66</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>昭公父公孫糾，糾父公子褍秦，褍秦即元公少子也。</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>auto-summary</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4537,7 +4555,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>简介：宋昭公之父。</t>
+          <t>简介：宋昭公之父。 人工判定：人工指定</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5107,6 +5125,2526 @@
       <c r="Q69" t="inlineStr">
         <is>
           <t>2026-10-01 00:15:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>649cf40acaae</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>p_hanwendi</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>文帝</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>p_hanjingdi</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>劉啟</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>简介：文帝之子，平七國之亂。</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>bee417f977f9</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>p_lvhou</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>呂后</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>p_hanhuidi</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>劉盈</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>简介：劉邦與呂后之子。；作廢：並列父母性別判錯（docs/28 P0-2），已改生成器按性別判 父/母</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>f77b4394a10a</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>p_hanyuandi</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>元帝</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>p_hanchengdi</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>劉驁</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>简介：元帝之子，寵趙飛燕姊妹，政歸外戚。</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>d34e099b6c42</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>p_hanxuandi</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>宣帝</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>p_hanyuandi</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>劉奭</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>简介：宣帝之子，好儒術，寵任石顯。</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>6b66cfa1b12f</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>p_simayan</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>武帝</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>p_simazhong</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>司馬衷</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>简介：字正度，武帝子。</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>47e2d113ec57</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>p_hanyuandi</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>元帝</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>p_hanaidi</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>劉欣</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>祖父</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>简介：元帝之孫，寵董賢，有斷袖之典。</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>83cc738e7e13</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>p_simashao2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>明帝</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>p_simayan2</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>司馬衍</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>简介：字世根，明帝子。</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>af4836f9969e</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>p_liuhu</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>劉祜</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>祖父</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>简介：章帝孫。</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>853dc4a9883e</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>p_liuzhao</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>劉肇</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>简介：章帝子。</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>7a55c551522f</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>p_simayan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>武帝</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>p_simazhi</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>司馬熾</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>简介：字丰度，武帝子。</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>69e3ea70cc9c</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>p_simarui</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>元帝</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>p_simashao2</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>司馬紹</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>简介：字道畿，元帝子。</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ed9ba0cfccde</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>p_hanyuandi</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>元帝</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>p_hanpingdi</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>劉衎</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>祖父</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>简介：元帝之孫，即位時王莽專權。</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>a5bb146d89f3</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>p_liuqing_hhs</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>劉慶</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>简介：章帝子。</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>81fbb0aa4f3e</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>p_liukai</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>劉開</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>简介：章帝子。</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>96f7fa1d9e6c</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>p_liuzhuang</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>明帝</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>p_liuchang2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>劉長</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>简介：明帝子。</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>b1b15e931fec</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>p_liuzhuang</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>明帝</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>p_liugong</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>劉恭</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>简介：明帝子。</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>081b5d7fbc36</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>p_liushu2</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>城陽懷王劉淑</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>简介：章帝子。</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>6d9350679639</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>p_liuxiu</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>光武</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>p_liuyan_ht</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>劉焉</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>简介：光武子。</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>76b79d27a133</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>p_liusheng_hhs</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>劉勝</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>简介：章帝子。</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3c4ea99e9fc1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>p_liuxiu</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>光武</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>p_liucang</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>劉蒼</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>简介：光武子。</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>51c021e8c46f</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>p_liuxiu</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>光武</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>p_liufu</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>劉輔</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>简介：光武子。</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>318253f37088</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>p_liuzhuang</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>明帝</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>p_liuxian_hhs</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>劉羨</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>简介：明帝子。</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>84bfad04b481</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>p_liuzhuang</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>明帝</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>p_liuyan3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>劉衍</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>简介：明帝子。</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>6b9a5528146f</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>p_liuzhuang</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>明帝</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>p_liudang</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>劉黨</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>简介：明帝子。</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>977da8ec3cd9</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>p_liuxiu</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>光武</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>p_liuyan2</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>劉延</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>简介：光武子。</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>095dbe83fa70</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>p_liji</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>驪姬</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>p_xiqi</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>奚齊</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>简介：晉獻公與驪姬之子，為裏克所殺。；作廢：並列父母性別判錯（docs/28 P0-2），已改生成器按性別判 父/母</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>114465a9065a</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>p_simadezong</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>安帝</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>p_simadewen</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>司馬德文</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>兄</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>简介：安帝弟。</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>7265a94e2f6c</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>p_liuzhuang</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>明帝</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>p_liubing2</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>劉昞</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>简介：明帝子。</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>98db0cce3e1a</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>p_liukang2</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>劉伉</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>简介：章帝子。</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cce57c381f84</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>p_liushou</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>劉壽</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>简介：章帝子。</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>b379679feff3</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>p_luyuangongzhu</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>魯元公主</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>p_luyuanwang</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>魯元王</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>简介：名張偃，張敖與魯元公主之子，呂后封為魯王。；作廢：並列父母性別判錯（docs/28 P0-2），已改生成器按性別判 父/母</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>bd2ae5ca9398</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>p_liuwansui</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>劉萬歲</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>简介：章帝子。</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0ba510df556a</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>p_liuzhuang</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>明帝</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>p_liujian_hhs</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>劉建</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>简介：明帝子。</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ac0893e9378d</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>p_hanwendi</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>文帝</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>p_liucan_hs</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>劉參</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>简介：文帝之子，初封太原王，後徙代。</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>13a1ffcad873</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>p_liuzhuang</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>明帝</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>p_liuchang_hhs</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>劉暢</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>简介：明帝子。</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>7338a726428b</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>p_liuxiu</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>光武</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>p_liujing2</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>劉京</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>简介：光武子。</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>5eff48d85ad0</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>p_liuda</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>章帝</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>p_liuquan</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>劉全</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>简介：章帝子。</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>fb9b880d61d3</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>p_liuxiu</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>光武</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>p_liukang</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>劉康</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>简介：光武子。</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>78b54d0c4992</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>p_liuxiu</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>光武</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>p_liujing_hhs</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>劉荊</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>简介：光武子。</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>9bd10ebb1758</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>p_liuxiu</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>光武</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>p_liuheng</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>劉衡</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>简介：光武子。</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:42:44</t>
         </is>
       </c>
     </row>
@@ -5121,7 +7659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6150,6 +8688,60 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4060d6c8bd5a</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>8634ecc807d8</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:39:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>b6081611ae10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>bc3b23e76a66</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>主证据</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:39:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbook/relations.xlsx
+++ b/workbook/relations.xlsx
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>p_x58047</t>
+          <t>p_hufen</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">

--- a/workbook/relations.xlsx
+++ b/workbook/relations.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2296f0696b2f</t>
+          <t>cd2679efd0cb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0431c8ee4e39</t>
+          <t>f7cd001e276b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -626,6 +626,11 @@
       <c r="H3" t="n">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>auto-summary</t>
@@ -653,7 +658,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>b38716070bcc</t>
+          <t>da7cd095d016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -689,6 +694,16 @@
       <c r="H4" t="n">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>西周</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>0dabbce7bd2a</t>
@@ -726,7 +741,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5c4991f48e19</t>
+          <t>d194ec263245</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -761,6 +776,16 @@
       </c>
       <c r="H5" t="n">
         <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>三國</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -799,7 +824,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17764e4d7149</t>
+          <t>cd2679efd0cb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -862,7 +887,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bee417f977f9</t>
+          <t>cfdd97b52de6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -925,7 +950,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2c4c83a3c13f</t>
+          <t>5c7e15e13f6e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -960,6 +985,16 @@
       </c>
       <c r="H8" t="n">
         <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -988,7 +1023,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>60f499b142ef</t>
+          <t>7a3703e735ee</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1023,6 +1058,16 @@
       </c>
       <c r="H9" t="n">
         <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1061,7 +1106,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>594820affdd0</t>
+          <t>63189ca81e90</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1096,6 +1141,16 @@
       </c>
       <c r="H10" t="n">
         <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>東晉</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1124,7 +1179,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>c678a3ac79cc</t>
+          <t>d836671bf796</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1159,6 +1214,16 @@
       </c>
       <c r="H11" t="n">
         <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1197,7 +1262,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3c72972d2f9c</t>
+          <t>0490572d52ed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1232,6 +1297,11 @@
       </c>
       <c r="H12" t="n">
         <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1260,7 +1330,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>304f2001cedd</t>
+          <t>4714f6b02c31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1295,6 +1365,16 @@
       </c>
       <c r="H13" t="n">
         <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>西周</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1333,7 +1413,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2078d05f6d16</t>
+          <t>7d222f86ed3d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1369,6 +1449,16 @@
       <c r="H14" t="n">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>戰國</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>9790fe5d27b8</t>
@@ -1406,7 +1496,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a02d1ec0804f</t>
+          <t>621cb0a20868</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1441,6 +1531,11 @@
       </c>
       <c r="H15" t="n">
         <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1469,7 +1564,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>be1b5211ef1f</t>
+          <t>7a2ac026c327</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1504,6 +1599,16 @@
       </c>
       <c r="H16" t="n">
         <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1542,7 +1647,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>43e7c6df851c</t>
+          <t>e1ae3766196e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1577,6 +1682,16 @@
       </c>
       <c r="H17" t="n">
         <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>戰國</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1605,7 +1720,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f4a897e40de2</t>
+          <t>1a6e90a6d635</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,6 +1755,16 @@
       </c>
       <c r="H18" t="n">
         <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>春秋</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1678,7 +1803,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ce43d453585a</t>
+          <t>e379c4876940</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1713,6 +1838,16 @@
       </c>
       <c r="H19" t="n">
         <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>商</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1751,7 +1886,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cd0f2e4cee20</t>
+          <t>02cf0846212e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1786,6 +1921,16 @@
       </c>
       <c r="H20" t="n">
         <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1814,7 +1959,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0041d2a87a1a</t>
+          <t>bd7958ec8ac6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1850,6 +1995,11 @@
       <c r="H21" t="n">
         <v>1</v>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>戰國</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>auto-summary</t>
@@ -1877,7 +2027,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>56cea1d3bc79</t>
+          <t>b1d0e1026dec</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1912,6 +2062,11 @@
       </c>
       <c r="H22" t="n">
         <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1940,7 +2095,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>672dcff37ed5</t>
+          <t>0e1d57f742bc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1976,6 +2131,16 @@
       <c r="H23" t="n">
         <v>1</v>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>f9a3c6c1d2d9</t>
@@ -2013,7 +2178,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2630cf047652</t>
+          <t>e38698a3d9c6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2048,6 +2213,11 @@
       </c>
       <c r="H24" t="n">
         <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2076,7 +2246,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>d5ad54ee2bb0</t>
+          <t>7927e73ebaad</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2111,6 +2281,16 @@
       </c>
       <c r="H25" t="n">
         <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>戰國</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2149,7 +2329,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26143b4b0b7e</t>
+          <t>a1e46c3baf74</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2184,6 +2364,11 @@
       </c>
       <c r="H26" t="n">
         <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>三國</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2212,7 +2397,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>c33396191064</t>
+          <t>9009a2ce2e31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2247,6 +2432,11 @@
       </c>
       <c r="H27" t="n">
         <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2275,7 +2465,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>c8f87e56e196</t>
+          <t>24c7eb0bd6c5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2310,6 +2500,16 @@
       </c>
       <c r="H28" t="n">
         <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2348,7 +2548,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>947974fe5e24</t>
+          <t>3e554dca138f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2383,6 +2583,11 @@
       </c>
       <c r="H29" t="n">
         <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>春秋</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2411,7 +2616,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>095dbe83fa70</t>
+          <t>1b5fbe98fd52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2474,7 +2679,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>55f7899668f8</t>
+          <t>84e3e69e3f4e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2510,6 +2715,16 @@
       <c r="H31" t="n">
         <v>1</v>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>西周</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>5ab10eb5eb7f</t>
@@ -2547,7 +2762,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>e04f5111ff9b</t>
+          <t>2fae205a5db9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2582,6 +2797,16 @@
       </c>
       <c r="H32" t="n">
         <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2610,7 +2835,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29f7917aa594</t>
+          <t>f66ae474f7c2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2645,6 +2870,16 @@
       </c>
       <c r="H33" t="n">
         <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2683,7 +2918,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4060d6c8bd5a</t>
+          <t>eb48093b2948</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2718,6 +2953,16 @@
       </c>
       <c r="H34" t="n">
         <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>西晉</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2756,7 +3001,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>25fae4c3e660</t>
+          <t>b65cf6f642f8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2791,6 +3036,16 @@
       </c>
       <c r="H35" t="n">
         <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>秦末</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2829,7 +3084,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>b9bbd151ef6f</t>
+          <t>580adcdd6acc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2864,6 +3119,16 @@
       </c>
       <c r="H36" t="n">
         <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2902,7 +3167,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>291b93841321</t>
+          <t>7fe61412c26d</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2937,6 +3202,11 @@
       </c>
       <c r="H37" t="n">
         <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2965,7 +3235,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>e6b7b0388d08</t>
+          <t>75754c3ffb50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3000,6 +3270,16 @@
       </c>
       <c r="H38" t="n">
         <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>春秋</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3038,7 +3318,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>56d8b05a2ff4</t>
+          <t>fbc36f81fa59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3074,6 +3354,11 @@
       <c r="H39" t="n">
         <v>1</v>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>戰國</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>auto-summary</t>
@@ -3101,7 +3386,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3ee751ec022b</t>
+          <t>497c94dedd92</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3136,6 +3421,16 @@
       </c>
       <c r="H40" t="n">
         <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>秦</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3174,7 +3469,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>03f6fbc1a2b8</t>
+          <t>a0fd165c4f0a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3210,6 +3505,16 @@
       <c r="H41" t="n">
         <v>1</v>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>秦</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>auto-summary</t>
@@ -3237,7 +3542,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>22c9ec54ff6d</t>
+          <t>a61d798d6d86</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3272,6 +3577,16 @@
       </c>
       <c r="H42" t="n">
         <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3310,7 +3625,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>127a1274d490</t>
+          <t>9bfa5f31dee5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3345,6 +3660,11 @@
       </c>
       <c r="H43" t="n">
         <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>三國</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3373,7 +3693,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8b180e1a5460</t>
+          <t>e23192caf338</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3408,6 +3728,16 @@
       </c>
       <c r="H44" t="n">
         <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3446,7 +3776,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>b379679feff3</t>
+          <t>f20da1254338</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3509,7 +3839,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>674d6f1b21b3</t>
+          <t>98dfbf3cc613</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3545,6 +3875,16 @@
       <c r="H46" t="n">
         <v>1</v>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>d89d727126c9</t>
@@ -3582,7 +3922,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7d7a81fbf4e3</t>
+          <t>40bcb37820b9</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3645,7 +3985,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6aeb9b2e282d</t>
+          <t>02a4fcffbac8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3680,6 +4020,11 @@
       </c>
       <c r="H48" t="n">
         <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3708,7 +4053,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7d85ad627dd2</t>
+          <t>435d313f3a7b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3743,6 +4088,16 @@
       </c>
       <c r="H49" t="n">
         <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3781,7 +4136,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>04e722951489</t>
+          <t>d6ffc1a5b02c</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3816,6 +4171,11 @@
       </c>
       <c r="H50" t="n">
         <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>春秋</t>
+        </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -3844,7 +4204,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12c88e64bc54</t>
+          <t>93000ef5f69c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3879,6 +4239,16 @@
       </c>
       <c r="H51" t="n">
         <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3917,7 +4287,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>513231982081</t>
+          <t>364c17cf2ecf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3952,6 +4322,16 @@
       </c>
       <c r="H52" t="n">
         <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3990,7 +4370,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>e5d8ea6f360d</t>
+          <t>739072d1413d</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4025,6 +4405,11 @@
       </c>
       <c r="H53" t="n">
         <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -4053,7 +4438,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6447d383f0d9</t>
+          <t>d3e0e4867b70</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4088,6 +4473,11 @@
       </c>
       <c r="H54" t="n">
         <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4116,7 +4506,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8c6c3c9ecfaa</t>
+          <t>491e28cad748</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4151,6 +4541,16 @@
       </c>
       <c r="H55" t="n">
         <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>春秋</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4179,7 +4579,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>37ac3c6bee55</t>
+          <t>8ab852239611</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4214,6 +4614,16 @@
       </c>
       <c r="H56" t="n">
         <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>戰國</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4242,7 +4652,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>58d517381a99</t>
+          <t>feb58782670e</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4278,6 +4688,16 @@
       <c r="H57" t="n">
         <v>1</v>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>春秋</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>auto-summary</t>
@@ -4305,7 +4725,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342dc567a405</t>
+          <t>c528c1c9e211</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4340,6 +4760,11 @@
       </c>
       <c r="H58" t="n">
         <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4368,7 +4793,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>e56bd1502bf7</t>
+          <t>07c572bf3e14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4403,6 +4828,16 @@
       </c>
       <c r="H59" t="n">
         <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>三國</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>sgz</t>
+        </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -4431,7 +4866,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9b2ff36f8bb8</t>
+          <t>82a7f49725ed</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4466,6 +4901,16 @@
       </c>
       <c r="H60" t="n">
         <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>春秋</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -4494,7 +4939,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>b6081611ae10</t>
+          <t>f80c1a4a145d</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4529,6 +4974,16 @@
       </c>
       <c r="H61" t="n">
         <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>春秋</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4567,7 +5022,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>c3c9b743e2de</t>
+          <t>63c99b5ef70d</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4602,6 +5057,16 @@
       </c>
       <c r="H62" t="n">
         <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4630,7 +5095,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>579ee52bae5e</t>
+          <t>8e32c91ff435</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4665,6 +5130,16 @@
       </c>
       <c r="H63" t="n">
         <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4703,7 +5178,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>b64517dc20ef</t>
+          <t>b12b845a881e</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4738,6 +5213,16 @@
       </c>
       <c r="H64" t="n">
         <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4776,7 +5261,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2296f0696b2f</t>
+          <t>cd2679efd0cb</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4859,7 +5344,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>84e131974ee2</t>
+          <t>5703a1ea112b</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4894,6 +5379,16 @@
       </c>
       <c r="H66" t="n">
         <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4932,7 +5427,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>b5f70ff6eb7f</t>
+          <t>6497fd00d84f</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4967,6 +5462,16 @@
       </c>
       <c r="H67" t="n">
         <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>春秋</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5005,7 +5510,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>c212cf2c0cd1</t>
+          <t>20b02ac19a92</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5040,6 +5545,16 @@
       </c>
       <c r="H68" t="n">
         <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>sj</t>
+        </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -5068,7 +5583,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6c89ba2115a3</t>
+          <t>5c10267ad67c</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5103,6 +5618,16 @@
       </c>
       <c r="H69" t="n">
         <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -5131,7 +5656,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>649cf40acaae</t>
+          <t>2746ce802727</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5166,6 +5691,11 @@
       </c>
       <c r="H70" t="n">
         <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -5194,7 +5724,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bee417f977f9</t>
+          <t>cfdd97b52de6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5257,7 +5787,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>f77b4394a10a</t>
+          <t>6b240aaab68d</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5292,6 +5822,16 @@
       </c>
       <c r="H72" t="n">
         <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -5320,7 +5860,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>d34e099b6c42</t>
+          <t>c19b9c13ce0d</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5355,6 +5895,16 @@
       </c>
       <c r="H73" t="n">
         <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -5383,7 +5933,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6b66cfa1b12f</t>
+          <t>40f80788530c</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5418,6 +5968,16 @@
       </c>
       <c r="H74" t="n">
         <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>西晉</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -5446,7 +6006,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>47e2d113ec57</t>
+          <t>39e205feafe5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5481,6 +6041,16 @@
       </c>
       <c r="H75" t="n">
         <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -5509,7 +6079,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>83cc738e7e13</t>
+          <t>57a472bc324e</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5544,6 +6114,16 @@
       </c>
       <c r="H76" t="n">
         <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>東晉</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -5572,7 +6152,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>af4836f9969e</t>
+          <t>77b31e666dbd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5607,6 +6187,16 @@
       </c>
       <c r="H77" t="n">
         <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -5635,7 +6225,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>853dc4a9883e</t>
+          <t>4412bdc6ca91</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5670,6 +6260,16 @@
       </c>
       <c r="H78" t="n">
         <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -5698,7 +6298,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7a55c551522f</t>
+          <t>f583d9715c00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5733,6 +6333,16 @@
       </c>
       <c r="H79" t="n">
         <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>西晉</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -5761,7 +6371,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>69e3ea70cc9c</t>
+          <t>b4fb4c82d6a3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5796,6 +6406,16 @@
       </c>
       <c r="H80" t="n">
         <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>東晉</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -5824,7 +6444,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ed9ba0cfccde</t>
+          <t>906719a45a13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5859,6 +6479,16 @@
       </c>
       <c r="H81" t="n">
         <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -5887,7 +6517,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>a5bb146d89f3</t>
+          <t>f3279aba63ac</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5922,6 +6552,16 @@
       </c>
       <c r="H82" t="n">
         <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -5950,7 +6590,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>81fbb0aa4f3e</t>
+          <t>c69b3c65f275</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5985,6 +6625,16 @@
       </c>
       <c r="H83" t="n">
         <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -6013,7 +6663,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>96f7fa1d9e6c</t>
+          <t>3cc8bc150ae6</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6048,6 +6698,16 @@
       </c>
       <c r="H84" t="n">
         <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -6076,7 +6736,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>b1b15e931fec</t>
+          <t>33acffa8bae0</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6111,6 +6771,16 @@
       </c>
       <c r="H85" t="n">
         <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -6139,7 +6809,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>081b5d7fbc36</t>
+          <t>b6ed4a57df97</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6174,6 +6844,16 @@
       </c>
       <c r="H86" t="n">
         <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -6202,7 +6882,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6d9350679639</t>
+          <t>1899198f9391</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6237,6 +6917,16 @@
       </c>
       <c r="H87" t="n">
         <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -6265,7 +6955,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>76b79d27a133</t>
+          <t>2c8af36add8e</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6300,6 +6990,16 @@
       </c>
       <c r="H88" t="n">
         <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -6328,7 +7028,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3c4ea99e9fc1</t>
+          <t>92a7753211dc</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6363,6 +7063,16 @@
       </c>
       <c r="H89" t="n">
         <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -6391,7 +7101,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>51c021e8c46f</t>
+          <t>69479423d86c</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6426,6 +7136,16 @@
       </c>
       <c r="H90" t="n">
         <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -6454,7 +7174,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>318253f37088</t>
+          <t>3c4e1af35914</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6489,6 +7209,16 @@
       </c>
       <c r="H91" t="n">
         <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -6517,7 +7247,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>84bfad04b481</t>
+          <t>f70e4dd2df75</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6552,6 +7282,16 @@
       </c>
       <c r="H92" t="n">
         <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -6580,7 +7320,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6b9a5528146f</t>
+          <t>b73939f6a807</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6615,6 +7355,16 @@
       </c>
       <c r="H93" t="n">
         <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -6643,7 +7393,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>977da8ec3cd9</t>
+          <t>43c762cf4208</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6678,6 +7428,16 @@
       </c>
       <c r="H94" t="n">
         <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -6706,7 +7466,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>095dbe83fa70</t>
+          <t>1b5fbe98fd52</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6769,7 +7529,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>114465a9065a</t>
+          <t>7668a3317c59</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6805,6 +7565,16 @@
       <c r="H96" t="n">
         <v>1</v>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>東晉</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>auto-summary</t>
@@ -6832,7 +7602,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7265a94e2f6c</t>
+          <t>2f26300f4ad7</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6867,6 +7637,16 @@
       </c>
       <c r="H97" t="n">
         <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -6895,7 +7675,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>98db0cce3e1a</t>
+          <t>5e58f0a5673f</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6930,6 +7710,16 @@
       </c>
       <c r="H98" t="n">
         <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -6958,7 +7748,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cce57c381f84</t>
+          <t>8c9b9b736192</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6993,6 +7783,16 @@
       </c>
       <c r="H99" t="n">
         <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -7021,7 +7821,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>b379679feff3</t>
+          <t>f20da1254338</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7084,7 +7884,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>bd2ae5ca9398</t>
+          <t>7614ecfc21eb</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7119,6 +7919,16 @@
       </c>
       <c r="H101" t="n">
         <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -7147,7 +7957,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0ba510df556a</t>
+          <t>14c2ba211bae</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7182,6 +7992,16 @@
       </c>
       <c r="H102" t="n">
         <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -7210,7 +8030,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ac0893e9378d</t>
+          <t>db0a6eeadcb0</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7245,6 +8065,16 @@
       </c>
       <c r="H103" t="n">
         <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>西漢</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>hs</t>
+        </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -7273,7 +8103,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>13a1ffcad873</t>
+          <t>0ec939bbe444</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7308,6 +8138,16 @@
       </c>
       <c r="H104" t="n">
         <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -7336,7 +8176,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7338a726428b</t>
+          <t>e5904c536926</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7371,6 +8211,16 @@
       </c>
       <c r="H105" t="n">
         <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -7399,7 +8249,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5eff48d85ad0</t>
+          <t>d7f97603e3ed</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7434,6 +8284,16 @@
       </c>
       <c r="H106" t="n">
         <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -7462,7 +8322,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>fb9b880d61d3</t>
+          <t>4f9d9c49165a</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7497,6 +8357,16 @@
       </c>
       <c r="H107" t="n">
         <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -7525,7 +8395,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>78b54d0c4992</t>
+          <t>4b0dcebae0ba</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7560,6 +8430,16 @@
       </c>
       <c r="H108" t="n">
         <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -7588,7 +8468,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9bd10ebb1758</t>
+          <t>d9c82d2b76fc</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7623,6 +8503,16 @@
       </c>
       <c r="H109" t="n">
         <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -7645,6 +8535,147 @@
       <c r="Q109" t="inlineStr">
         <is>
           <t>2026-10-01 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>21d3f1e22e38</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>p_liuhu</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>安帝</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>p_liubao</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>劉保</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>東漢</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>简介：安帝子。</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>2026-10-04 17:43:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>68bb0ad091d9</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>p_yanyiwang</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>燕易王</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>p_yanwangkuai</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>名噲</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>kinship</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>戰國</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>auto-summary</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>简介：名噲之父，燕稱王自易王始。</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>2026-10-04 17:43:13</t>
         </is>
       </c>
     </row>
@@ -7692,7 +8723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2078d05f6d16</t>
+          <t>7d222f86ed3d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7719,7 +8750,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>e6b7b0388d08</t>
+          <t>75754c3ffb50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7746,7 +8777,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>b38716070bcc</t>
+          <t>da7cd095d016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7773,7 +8804,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>b38716070bcc</t>
+          <t>da7cd095d016</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7800,7 +8831,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5c4991f48e19</t>
+          <t>d194ec263245</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7827,7 +8858,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>60f499b142ef</t>
+          <t>7a3703e735ee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7854,7 +8885,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>60f499b142ef</t>
+          <t>7a3703e735ee</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7881,7 +8912,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>c678a3ac79cc</t>
+          <t>d836671bf796</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7908,7 +8939,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>304f2001cedd</t>
+          <t>4714f6b02c31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7935,7 +8966,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>be1b5211ef1f</t>
+          <t>7a2ac026c327</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7962,7 +8993,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f4a897e40de2</t>
+          <t>1a6e90a6d635</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7989,7 +9020,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ce43d453585a</t>
+          <t>e379c4876940</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8016,7 +9047,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ce43d453585a</t>
+          <t>e379c4876940</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8043,7 +9074,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>672dcff37ed5</t>
+          <t>0e1d57f742bc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8070,7 +9101,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>672dcff37ed5</t>
+          <t>0e1d57f742bc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8097,7 +9128,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>d5ad54ee2bb0</t>
+          <t>7927e73ebaad</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8124,7 +9155,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>c8f87e56e196</t>
+          <t>24c7eb0bd6c5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8151,7 +9182,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>55f7899668f8</t>
+          <t>84e3e69e3f4e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8178,7 +9209,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>55f7899668f8</t>
+          <t>84e3e69e3f4e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8205,7 +9236,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29f7917aa594</t>
+          <t>f66ae474f7c2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8232,7 +9263,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25fae4c3e660</t>
+          <t>b65cf6f642f8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8259,7 +9290,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>b9bbd151ef6f</t>
+          <t>580adcdd6acc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8286,7 +9317,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b9bbd151ef6f</t>
+          <t>580adcdd6acc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8313,7 +9344,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3ee751ec022b</t>
+          <t>497c94dedd92</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8340,7 +9371,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>22c9ec54ff6d</t>
+          <t>a61d798d6d86</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8367,7 +9398,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8b180e1a5460</t>
+          <t>e23192caf338</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8394,7 +9425,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>674d6f1b21b3</t>
+          <t>98dfbf3cc613</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8421,7 +9452,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7d85ad627dd2</t>
+          <t>435d313f3a7b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8448,7 +9479,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7d85ad627dd2</t>
+          <t>435d313f3a7b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8475,7 +9506,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12c88e64bc54</t>
+          <t>93000ef5f69c</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8502,7 +9533,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>513231982081</t>
+          <t>364c17cf2ecf</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8529,7 +9560,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>579ee52bae5e</t>
+          <t>8e32c91ff435</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8556,7 +9587,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b64517dc20ef</t>
+          <t>b12b845a881e</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8583,7 +9614,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2296f0696b2f</t>
+          <t>cd2679efd0cb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8610,7 +9641,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>84e131974ee2</t>
+          <t>5703a1ea112b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8637,7 +9668,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>b5f70ff6eb7f</t>
+          <t>6497fd00d84f</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8664,7 +9695,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>b5f70ff6eb7f</t>
+          <t>6497fd00d84f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8691,7 +9722,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4060d6c8bd5a</t>
+          <t>eb48093b2948</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8718,7 +9749,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>b6081611ae10</t>
+          <t>f80c1a4a145d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
